--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_42.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3409383.021783935</v>
+        <v>3445741.068091149</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117051322</v>
+        <v>603.5370117101701</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117051322</v>
+        <v>603.5370117101701</v>
       </c>
     </row>
     <row r="11">
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>68.52661386969099</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,22 +778,22 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
         <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>374</v>
       </c>
       <c r="T3" t="n">
-        <v>374</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>242.2880781462008</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -909,10 +909,10 @@
         <v>3.347322035759929</v>
       </c>
       <c r="H5" t="n">
-        <v>3.810231567849018</v>
+        <v>5.608919435675665</v>
       </c>
       <c r="I5" t="n">
-        <v>1.798687867826647</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>367.4148868884558</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1021,10 +1021,10 @@
         <v>133.6519859716246</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536602</v>
       </c>
       <c r="T6" t="n">
-        <v>6.631692609440937</v>
+        <v>4.473444462796834</v>
       </c>
       <c r="U6" t="n">
         <v>0.1959257979225968</v>
@@ -1219,10 +1219,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>150.4346265429118</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1261,7 +1261,7 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>349.4707841021626</v>
       </c>
       <c r="U9" t="n">
         <v>0.1959257979225981</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T11" t="n">
         <v>259.6218731858503</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>200.5295027796755</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,16 +1495,16 @@
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V12" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
@@ -1513,7 +1513,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,13 +1565,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
         <v>30.56285675203577</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1684,25 +1684,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
-        <v>173.591815881973</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1726,22 +1726,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490372</v>
+        <v>174.1249482875297</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,16 +1802,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T17" t="n">
         <v>259.6218731858503</v>
@@ -1921,16 +1921,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1978,10 +1978,10 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>267.1024830734931</v>
       </c>
       <c r="W18" t="n">
-        <v>284.9649587918016</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>419.8627394453875</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2145,7 +2145,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>190.3174326828064</v>
+        <v>190.7780200481207</v>
       </c>
     </row>
     <row r="21">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>21.67209722191262</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
@@ -2218,13 +2218,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>284.9649587918013</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2279,10 +2279,10 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q22" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R22" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
         <v>30.56285675203577</v>
@@ -2361,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T23" t="n">
         <v>259.6218731858503</v>
@@ -2395,16 +2395,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.999611346725456</v>
@@ -2452,16 +2452,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>267.1024830734933</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2641,13 +2641,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>177.6137898608475</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,19 +2677,19 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>353.9253867592582</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
@@ -2875,16 +2875,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H30" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
@@ -3121,7 +3121,7 @@
         <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,16 +3148,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
-        <v>254.9671660051475</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
         <v>79.16168051490372</v>
@@ -3221,10 +3221,10 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O34" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627037</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
@@ -3282,7 +3282,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U35" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V35" t="n">
         <v>308.8510241668239</v>
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038857</v>
       </c>
       <c r="F36" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>177.5914272286986</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
         <v>4.021973978873961</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3470,7 +3470,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H38" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U38" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V38" t="n">
         <v>308.8510241668239</v>
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>177.5914272286985</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H39" t="n">
         <v>4.021973978873961</v>
@@ -3637,16 +3637,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W39" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3753,7 +3753,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T41" t="n">
         <v>259.6218731858503</v>
@@ -3817,16 +3817,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>3.99961134672543</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T42" t="n">
-        <v>254.9671660051475</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
         <v>79.16168051490371</v>
@@ -3880,7 +3880,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3926,7 +3926,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N43" t="n">
         <v>155.2579933044718</v>
@@ -3935,7 +3935,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>26.93768689770263</v>
@@ -4066,7 +4066,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>177.5914272286987</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H45" t="n">
         <v>4.021973978873961</v>
@@ -4114,7 +4114,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>98.86273944538755</v>
@@ -4172,7 +4172,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
@@ -4181,7 +4181,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090252216</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>886.1402453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1256.400245326633</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1314.492137192891</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244.8234770117097</v>
+        <v>761.3300353983303</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>692.1112335097536</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>363.3030116424684</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>29.92</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.92</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>833.4673281331341</v>
       </c>
       <c r="T3" t="n">
-        <v>920.1002047909187</v>
+        <v>828.9486973626322</v>
       </c>
       <c r="U3" t="n">
-        <v>542.3224270131409</v>
+        <v>828.7507925162457</v>
       </c>
       <c r="V3" t="n">
-        <v>297.586994542231</v>
+        <v>814.0935529288516</v>
       </c>
       <c r="W3" t="n">
-        <v>264.8868501888688</v>
+        <v>781.3934085754895</v>
       </c>
       <c r="X3" t="n">
-        <v>244.8234770117097</v>
+        <v>761.3300353983303</v>
       </c>
       <c r="Y3" t="n">
-        <v>244.8234770117097</v>
+        <v>761.3300353983303</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>618.7389978118695</v>
+        <v>276.481125097303</v>
       </c>
       <c r="C4" t="n">
-        <v>618.7389978118695</v>
+        <v>276.481125097303</v>
       </c>
       <c r="D4" t="n">
-        <v>618.7389978118695</v>
+        <v>276.481125097303</v>
       </c>
       <c r="E4" t="n">
-        <v>618.7389978118695</v>
+        <v>276.481125097303</v>
       </c>
       <c r="F4" t="n">
-        <v>618.7389978118695</v>
+        <v>333.6297652012307</v>
       </c>
       <c r="G4" t="n">
-        <v>618.7389978118695</v>
+        <v>487.2184261700831</v>
       </c>
       <c r="H4" t="n">
-        <v>789.8745737909392</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.483548464727</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>259.1973975316665</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V4" t="n">
-        <v>259.1973975316665</v>
+        <v>276.481125097303</v>
       </c>
       <c r="W4" t="n">
-        <v>431.0883157913439</v>
+        <v>276.481125097303</v>
       </c>
       <c r="X4" t="n">
-        <v>507.3296971328372</v>
+        <v>276.481125097303</v>
       </c>
       <c r="Y4" t="n">
-        <v>618.7389978118695</v>
+        <v>276.481125097303</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>35.58557518755118</v>
       </c>
       <c r="H5" t="n">
-        <v>31.73685643214813</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4567,16 +4567,16 @@
         <v>1067.648108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>381.3722089875785</v>
+        <v>704.8616534045707</v>
       </c>
       <c r="C6" t="n">
-        <v>381.3722089875785</v>
+        <v>704.8616534045707</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>704.8616534045707</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G6" t="n">
         <v>29.92</v>
@@ -4664,25 +4664,25 @@
         <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>833.4673281331338</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>826.7686487296581</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>826.5707438832717</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>811.9135042958776</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>779.2133599425155</v>
+        <v>1096.051174953907</v>
       </c>
       <c r="X6" t="n">
-        <v>759.1499867653563</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>759.1499867653563</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>822.5694727264984</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C7" t="n">
-        <v>822.5694727264984</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D7" t="n">
-        <v>935.8886168514985</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E7" t="n">
-        <v>1053.717521062911</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F7" t="n">
-        <v>1178.078493654847</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="G7" t="n">
-        <v>1178.078493654847</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="H7" t="n">
-        <v>1178.078493654847</v>
+        <v>1024.853581566337</v>
       </c>
       <c r="I7" t="n">
-        <v>1255.22297682294</v>
+        <v>1251.462556240125</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.22297682294</v>
+        <v>1251.462556240125</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4749,19 +4749,19 @@
         <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>448.3720433569805</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>599.402834381174</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>710.8121350602063</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="8">
@@ -4795,22 +4795,22 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>451.8183303517587</v>
+        <v>755.48</v>
       </c>
       <c r="M8" t="n">
-        <v>822.0783303517587</v>
+        <v>755.48</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>727.505640524864</v>
       </c>
       <c r="C9" t="n">
-        <v>1222.526720202428</v>
+        <v>727.505640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>871.07451121485</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>524.9410796775644</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>181.8741682251635</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>795.1243024891659</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>794.9263976427794</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>780.2691580553853</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>747.5690137020232</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>727.505640524864</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>727.505640524864</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>504.674685712814</v>
+        <v>774.8297405151413</v>
       </c>
       <c r="C10" t="n">
-        <v>504.674685712814</v>
+        <v>900.8317463335771</v>
       </c>
       <c r="D10" t="n">
-        <v>504.674685712814</v>
+        <v>1014.150890458577</v>
       </c>
       <c r="E10" t="n">
-        <v>575.7683720264802</v>
+        <v>1131.97979466999</v>
       </c>
       <c r="F10" t="n">
-        <v>700.1293446184156</v>
+        <v>1256.340767261926</v>
       </c>
       <c r="G10" t="n">
-        <v>853.7180055872682</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="K10" t="n">
         <v>1382.983127881912</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>70.34367574991084</v>
+        <v>228.741392885946</v>
       </c>
       <c r="W10" t="n">
-        <v>242.2345940095882</v>
+        <v>400.6323111456234</v>
       </c>
       <c r="X10" t="n">
-        <v>393.2653850337817</v>
+        <v>551.6631021698169</v>
       </c>
       <c r="Y10" t="n">
-        <v>504.674685712814</v>
+        <v>663.0724028488492</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D11" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H11" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
@@ -5035,22 +5035,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L11" t="n">
-        <v>991.9887866314309</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M11" t="n">
-        <v>1634.498786631431</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N11" t="n">
-        <v>2238.277892278425</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O11" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5059,25 +5059,25 @@
         <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="12">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.9377012410212</v>
+        <v>343.7981213238219</v>
       </c>
       <c r="C12" t="n">
-        <v>452.1903149324157</v>
+        <v>303.2931592576408</v>
       </c>
       <c r="D12" t="n">
         <v>100.7381059448373</v>
@@ -5099,10 +5099,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5138,25 +5138,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>699.5393655335968</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>587.0412413822548</v>
       </c>
       <c r="X12" t="n">
-        <v>1459.907161134389</v>
+        <v>487.1798884071159</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.378667550442</v>
+        <v>407.9966633908185</v>
       </c>
     </row>
     <row r="13">
@@ -5196,22 +5196,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
         <v>82.79157247680381</v>
@@ -5245,40 +5245,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C14" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D14" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E14" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G14" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>310.7478922784252</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>953.2578922784252</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L14" t="n">
+        <v>953.2578922784251</v>
+      </c>
+      <c r="M14" t="n">
         <v>1595.767892278425</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2238.277892278425</v>
       </c>
       <c r="N14" t="n">
         <v>2238.277892278425</v>
@@ -5305,16 +5305,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W14" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="15">
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1316.525394051095</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C15" t="n">
-        <v>951.7780077424895</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D15" t="n">
-        <v>924.5682229973354</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E15" t="n">
-        <v>578.4347914600498</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>235.3678800076489</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
-        <v>227.2652685676495</v>
+        <v>51.92</v>
       </c>
       <c r="I15" t="n">
         <v>51.92</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R15" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1118.775526742765</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V15" t="n">
-        <v>1672.26663826087</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118092</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="16">
@@ -5445,13 +5445,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,40 +5482,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L17" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M17" t="n">
-        <v>1634.498786631431</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N17" t="n">
         <v>1651.83297330616</v>
@@ -5533,25 +5533,25 @@
         <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.6952769985968</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C18" t="n">
-        <v>127.9478906899915</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E18" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5621,16 +5621,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V18" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W18" t="n">
-        <v>1060.180821299454</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X18" t="n">
-        <v>636.0770440818907</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y18" t="n">
-        <v>556.8938190655933</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5743,49 +5743,49 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L20" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M20" t="n">
-        <v>2060.956838088718</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N20" t="n">
-        <v>2060.956838088718</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="O20" t="n">
-        <v>2222.086939471673</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P20" t="n">
-        <v>2418.678945810293</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
         <v>759.2809169713448</v>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>492.6952769985968</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D21" t="n">
         <v>100.7381059448373</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R21" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U21" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V21" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W21" t="n">
-        <v>1384.423245541878</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X21" t="n">
-        <v>960.3194683243149</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y21" t="n">
-        <v>556.8938190655933</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="22">
@@ -5922,7 +5922,7 @@
         <v>819.9299076645211</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R22" t="n">
         <v>82.79157247680381</v>
@@ -5992,19 +5992,19 @@
         <v>2060.956838088718</v>
       </c>
       <c r="N23" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>2222.086939471673</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
-        <v>2418.678945810293</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
         <v>2451.762030971221</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.02261143999941</v>
@@ -6095,16 +6095,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q25" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R25" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,46 +6193,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C26" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D26" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E26" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G26" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>989.863031102066</v>
       </c>
       <c r="L26" t="n">
-        <v>991.9887866314309</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M26" t="n">
-        <v>1009.32297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N26" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O26" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P26" t="n">
         <v>2009.555081027735</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>168.4528527561725</v>
+        <v>668.0405455662468</v>
       </c>
       <c r="C27" t="n">
-        <v>127.9478906899915</v>
+        <v>627.5355835000657</v>
       </c>
       <c r="D27" t="n">
-        <v>100.7381059448373</v>
+        <v>600.3257987549116</v>
       </c>
       <c r="E27" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600504</v>
       </c>
       <c r="F27" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076495</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>231.3278685463106</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6320,28 +6320,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1886.686949702618</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S27" t="n">
-        <v>1429.292781642309</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T27" t="n">
-        <v>1347.095458285567</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U27" t="n">
-        <v>942.8917405937455</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V27" t="n">
-        <v>524.1940969659473</v>
+        <v>1023.781789776022</v>
       </c>
       <c r="W27" t="n">
-        <v>411.6959728146054</v>
+        <v>911.2836656246797</v>
       </c>
       <c r="X27" t="n">
-        <v>311.8346198394665</v>
+        <v>811.4223126495407</v>
       </c>
       <c r="Y27" t="n">
-        <v>232.6513948231691</v>
+        <v>732.2390876332433</v>
       </c>
     </row>
     <row r="28">
@@ -6454,25 +6454,25 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>950.0896384907273</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.599638490728</v>
+        <v>1149.849898617045</v>
       </c>
       <c r="N29" t="n">
-        <v>1651.83297330616</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O29" t="n">
-        <v>1812.963074689115</v>
+        <v>1953.49</v>
       </c>
       <c r="P29" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6518,13 +6518,13 @@
         <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>727.3319471348246</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
         <v>384.2650356824237</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6691,22 +6691,22 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1166.141587033441</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P32" t="n">
         <v>2009.555081027735</v>
@@ -6724,19 +6724,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>492.6952769985969</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C33" t="n">
-        <v>452.1903149324158</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872616</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F33" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R33" t="n">
-        <v>1737.789794027844</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S33" t="n">
-        <v>1280.395625967535</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T33" t="n">
-        <v>1022.853034043143</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U33" t="n">
-        <v>942.8917405937456</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V33" t="n">
-        <v>848.4365212083717</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W33" t="n">
-        <v>735.9383970570298</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X33" t="n">
-        <v>636.0770440818908</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y33" t="n">
-        <v>556.8938190655934</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="34">
@@ -6864,7 +6864,7 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
         <v>820.7766206439126</v>
@@ -6904,49 +6904,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O35" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6961,19 +6961,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>343.7981213238223</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C36" t="n">
-        <v>303.2931592576412</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D36" t="n">
-        <v>276.083374512487</v>
+        <v>276.0833745124868</v>
       </c>
       <c r="E36" t="n">
-        <v>254.1923672176257</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
-        <v>235.3678800076491</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G36" t="n">
         <v>55.98259997866057</v>
@@ -7031,28 +7031,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1280.395625967535</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1198.198302610793</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>793.994584918971</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>699.5393655335971</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>587.0412413822552</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>487.1798884071162</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>407.9966633908189</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7092,25 +7092,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M37" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N37" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O37" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C38" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D38" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E38" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G38" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H38" t="n">
         <v>51.92</v>
@@ -7168,22 +7168,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M38" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N38" t="n">
-        <v>1808.651587033441</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O38" t="n">
-        <v>1969.781688416396</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P38" t="n">
-        <v>2166.373694755016</v>
+        <v>2596</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7198,19 +7198,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W38" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X38" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="39">
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>343.7981213238222</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C39" t="n">
-        <v>303.293159257641</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D39" t="n">
-        <v>276.0833745124868</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E39" t="n">
-        <v>254.1923672176256</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
-        <v>235.367880007649</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
         <v>55.98259997866057</v>
@@ -7280,16 +7280,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W39" t="n">
-        <v>1235.526089867104</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X39" t="n">
-        <v>811.4223126495403</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y39" t="n">
-        <v>407.9966633908188</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="40">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7402,25 +7402,25 @@
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.143276253736</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N41" t="n">
-        <v>2234.653276253736</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>2395.783377636692</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2592.375383975311</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7429,25 +7429,25 @@
         <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C42" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D42" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E42" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F42" t="n">
         <v>60.0226114399994</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S42" t="n">
-        <v>1280.395625967535</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1022.853034043143</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U42" t="n">
-        <v>942.8917405937456</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>848.4365212083717</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W42" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X42" t="n">
-        <v>311.8346198394665</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y42" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="43">
@@ -7569,13 +7569,13 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P43" t="n">
         <v>820.7766206439126</v>
@@ -7639,25 +7639,25 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L44" t="n">
-        <v>1417.990475851726</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M44" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N44" t="n">
-        <v>1651.83297330616</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>992.2829698086708</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C45" t="n">
-        <v>951.7780077424898</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D45" t="n">
-        <v>924.5682229973356</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E45" t="n">
-        <v>578.4347914600501</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F45" t="n">
-        <v>235.3678800076491</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G45" t="n">
         <v>55.98259997866057</v>
@@ -7757,13 +7757,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1135.664736891965</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
-        <v>1056.481511875667</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="46">
@@ -7797,31 +7797,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611952</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.08070002423</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405841</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468673</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.40172660557</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111781</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076646058</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425882442</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949749713</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>720.3111720492747</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>311.8831458198699</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,7 +8210,7 @@
         <v>235.5012052109776</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
         <v>404.0826666125488</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748744</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N8" t="n">
-        <v>652.1329472004106</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q8" t="n">
         <v>502.5418702571336</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>840.3699380391354</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>179.1121759491998</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>248.0013330166451</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
         <v>230.4920535472222</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q20" t="n">
-        <v>202.5956441962828</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9635,7 +9635,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>230.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>202.5956441962828</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>318.9437086192779</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>950.4344291498551</v>
+        <v>503.6734416380457</v>
       </c>
       <c r="N29" t="n">
-        <v>290.3237048759414</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N32" t="n">
-        <v>721.0894134186553</v>
+        <v>489.3624610129226</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,10 +10571,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>290.7846768324985</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,13 +10811,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N38" t="n">
         <v>879.4920535472222</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>457.4494331410071</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27.14469655484982</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M44" t="n">
-        <v>537.6389720331213</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23429,7 +23429,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24137,10 +24137,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -25079,10 +25079,10 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.8382458495973992</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -25307,7 +25307,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25793,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -26030,7 +26030,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.8382458495973992</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495136049</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26269,25 +26269,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="C2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="D2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="F2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="G2" t="n">
         <v>1322324.768553815</v>
       </c>
       <c r="H2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="I2" t="n">
         <v>1322324.768553815</v>
@@ -26311,7 +26311,7 @@
         <v>1322324.768553814</v>
       </c>
       <c r="P2" t="n">
-        <v>1322324.768553817</v>
+        <v>1322324.768553815</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.493408911</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>455192.5576824596</v>
+        <v>461693.9226154357</v>
       </c>
       <c r="C6" t="n">
-        <v>688299.4798699484</v>
+        <v>694800.8448029248</v>
       </c>
       <c r="D6" t="n">
-        <v>690311.127285772</v>
+        <v>696812.4922187485</v>
       </c>
       <c r="E6" t="n">
-        <v>168891.2397576401</v>
+        <v>175354.2308879936</v>
       </c>
       <c r="F6" t="n">
-        <v>760127.3025758629</v>
+        <v>766590.2937062165</v>
       </c>
       <c r="G6" t="n">
-        <v>761815.6920975158</v>
+        <v>768278.6832278698</v>
       </c>
       <c r="H6" t="n">
-        <v>763506.4250074782</v>
+        <v>769969.416137832</v>
       </c>
       <c r="I6" t="n">
-        <v>765199.5182080262</v>
+        <v>771662.5093383804</v>
       </c>
       <c r="J6" t="n">
-        <v>378446.9888229509</v>
+        <v>384909.9799533049</v>
       </c>
       <c r="K6" t="n">
-        <v>768592.8542017839</v>
+        <v>775055.8453321381</v>
       </c>
       <c r="L6" t="n">
-        <v>770293.1319241283</v>
+        <v>776756.1230544825</v>
       </c>
       <c r="M6" t="n">
-        <v>675195.839804096</v>
+        <v>681658.8309344497</v>
       </c>
       <c r="N6" t="n">
-        <v>773700.9958948599</v>
+        <v>780163.9870252135</v>
       </c>
       <c r="O6" t="n">
-        <v>518608.6184933208</v>
+        <v>525071.6096236752</v>
       </c>
       <c r="P6" t="n">
-        <v>777118.7261449061</v>
+        <v>783581.7172752592</v>
       </c>
     </row>
   </sheetData>
@@ -26984,13 +26984,13 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27002,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27103,7 +27103,7 @@
         <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>292.5732985758283</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,22 +27557,22 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
+        <v>88.48881128536601</v>
+      </c>
+      <c r="T3" t="n">
         <v>400</v>
       </c>
-      <c r="T3" t="n">
-        <v>30.47344446279683</v>
-      </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>172.2225890453193</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27603,10 +27603,10 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>332.1087550626183</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27618,7 +27618,7 @@
         <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T4" t="n">
+        <v>209.2386648669134</v>
+      </c>
+      <c r="U4" t="n">
         <v>400</v>
-      </c>
-      <c r="T4" t="n">
-        <v>400</v>
-      </c>
-      <c r="U4" t="n">
-        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>324.4551417346462</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321734</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033002</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27749,22 +27749,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>17.14166975787083</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>330.0491815260438</v>
@@ -27800,10 +27800,10 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>397.8417518533559</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27831,7 +27831,7 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27840,16 +27840,16 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>367.7672216878439</v>
       </c>
       <c r="G7" t="n">
         <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>249.0257661558644</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
@@ -27858,7 +27858,7 @@
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27885,13 +27885,13 @@
         <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27998,10 +27998,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>175.0855131057004</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>55.00266036063425</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>352.7927091941951</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>372.781514799125</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
         <v>209.2386648669134</v>
@@ -28125,7 +28125,7 @@
         <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
@@ -28274,16 +28274,16 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
@@ -28292,7 +28292,7 @@
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28399,10 +28399,10 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28463,16 +28463,16 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28481,7 +28481,7 @@
         <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>18.05909831126235</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28505,22 +28505,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>226.036732227374</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28669,7 +28669,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
@@ -28700,16 +28700,16 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28757,10 +28757,10 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="W18" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28924,7 +28924,7 @@
         <v>321</v>
       </c>
       <c r="Y20" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
     </row>
     <row r="21">
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28997,13 +28997,13 @@
         <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29140,10 +29140,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T23" t="n">
         <v>321</v>
@@ -29174,16 +29174,16 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29420,13 +29420,13 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>147.4081841180265</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29456,19 +29456,19 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
-        <v>147.4081841180267</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
@@ -29654,16 +29654,16 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29860,7 +29860,7 @@
         <v>321</v>
       </c>
       <c r="U32" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V32" t="n">
         <v>321</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29900,7 +29900,7 @@
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I33" t="n">
         <v>191.6509141932353</v>
@@ -29927,16 +29927,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30097,7 +30097,7 @@
         <v>321</v>
       </c>
       <c r="U35" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V35" t="n">
         <v>321</v>
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="F36" t="n">
         <v>321</v>
       </c>
       <c r="G36" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="H36" t="n">
         <v>321</v>
@@ -30167,16 +30167,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V36" t="n">
         <v>321</v>
@@ -30295,7 +30295,7 @@
         <v>321</v>
       </c>
       <c r="H38" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I38" t="n">
         <v>96.76634561233286</v>
@@ -30334,7 +30334,7 @@
         <v>321</v>
       </c>
       <c r="U38" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V38" t="n">
         <v>321</v>
@@ -30356,22 +30356,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>321</v>
       </c>
       <c r="G39" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="H39" t="n">
         <v>321</v>
@@ -30416,16 +30416,16 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W39" t="n">
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30565,7 +30565,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T41" t="n">
         <v>321</v>
@@ -30596,16 +30596,16 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30641,13 +30641,13 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T42" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="U42" t="n">
         <v>321</v>
@@ -30659,7 +30659,7 @@
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>321</v>
@@ -30845,7 +30845,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="H45" t="n">
         <v>321</v>
@@ -30893,7 +30893,7 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
         <v>321</v>
@@ -30933,7 +30933,7 @@
         <v>321</v>
       </c>
       <c r="J46" t="n">
-        <v>321.0000000000855</v>
+        <v>321</v>
       </c>
       <c r="K46" t="n">
         <v>321</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>374</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.3412755627363</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34889,10 +34889,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>57.72589909487638</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
         <v>172.8642181606765</v>
@@ -34904,7 +34904,7 @@
         <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>77.0114963045387</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34989,7 +34989,7 @@
         <v>300.2102102361032</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,7 +35117,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35126,16 +35126,16 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>93.384365720102</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>77.92372037181164</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35144,7 +35144,7 @@
         <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35171,13 +35171,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
+        <v>306.7289592406478</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>374</v>
-      </c>
-      <c r="M8" t="n">
-        <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>248.0502805878619</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>71.81180435723857</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>127.9215763838245</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3.798404629106074</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35411,7 +35411,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35457,16 +35457,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L11" t="n">
         <v>649</v>
-      </c>
-      <c r="L11" t="n">
-        <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35475,7 +35475,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>261.4423154327527</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L14" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
         <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
         <v>218.2342914572864</v>
@@ -35940,7 +35940,7 @@
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>17.50927946942293</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L20" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>421.6280856303014</v>
+      </c>
+      <c r="P20" t="n">
         <v>649</v>
       </c>
-      <c r="L20" t="n">
-        <v>649</v>
-      </c>
-      <c r="M20" t="n">
-        <v>649</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>162.757678164601</v>
-      </c>
-      <c r="P20" t="n">
-        <v>198.5777841804241</v>
-      </c>
       <c r="Q20" t="n">
-        <v>179.1121759491994</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36414,7 +36414,7 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>434.7823270636903</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>17.50927946942293</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q26" t="n">
         <v>592.3686050224903</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M29" t="n">
+        <v>202.2390124881908</v>
+      </c>
+      <c r="N29" t="n">
         <v>649</v>
-      </c>
-      <c r="M29" t="n">
-        <v>649</v>
-      </c>
-      <c r="N29" t="n">
-        <v>59.83165132871924</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q29" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
         <v>175.9119195979899</v>
@@ -37122,16 +37122,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>490.5973598714331</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q32" t="n">
         <v>592.3686050224903</v>
@@ -37350,10 +37350,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
@@ -37362,7 +37362,7 @@
         <v>649</v>
       </c>
       <c r="N35" t="n">
-        <v>60.29262328527629</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37590,13 +37590,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N38" t="n">
         <v>649</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
@@ -37836,7 +37836,7 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.661228307766413</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M44" t="n">
-        <v>236.2045428832663</v>
+        <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J46" t="n">
-        <v>329.5882314920466</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K46" t="n">
         <v>104.5500458709881</v>
